--- a/baseline_code/Data/Planes.xlsx
+++ b/baseline_code/Data/Planes.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70B7596-3657-42CB-BBA1-ED0A943F2544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <r>
       <rPr>
         <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Plane</t>
     </r>
@@ -27,6 +31,9 @@
     <r>
       <rPr>
         <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Gate</t>
     </r>
@@ -35,6 +42,9 @@
     <r>
       <rPr>
         <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>SIBT</t>
     </r>
@@ -43,6 +53,9 @@
     <r>
       <rPr>
         <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Cargo From</t>
     </r>
@@ -51,6 +64,9 @@
     <r>
       <rPr>
         <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Cargo To</t>
     </r>
@@ -59,231 +75,68 @@
     <t>LH997</t>
   </si>
   <si>
-    <r>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>33</t>
-    </r>
-  </si>
-  <si>
     <t>AF782</t>
   </si>
   <si>
-    <r>
-      <t>9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>66</t>
-    </r>
-  </si>
-  <si>
     <t>U28672</t>
   </si>
   <si>
-    <r>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>76</t>
-    </r>
-  </si>
-  <si>
     <t>LH412</t>
   </si>
   <si>
-    <r>
-      <t>12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>108</t>
-    </r>
-  </si>
-  <si>
     <t>EK533</t>
   </si>
   <si>
-    <r>
-      <t>13</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>122</t>
-    </r>
-  </si>
-  <si>
     <t>KL642</t>
   </si>
   <si>
-    <r>
-      <t>15</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>141</t>
-    </r>
-  </si>
-  <si>
     <t>BA774</t>
   </si>
   <si>
-    <r>
-      <t>16</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>170</t>
-    </r>
-  </si>
-  <si>
     <t>IB204</t>
   </si>
   <si>
-    <r>
-      <t>18</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>250</t>
-    </r>
-  </si>
-  <si>
     <t>AF1341</t>
   </si>
   <si>
-    <r>
-      <t>19</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>274</t>
-    </r>
-  </si>
-  <si>
     <t>TK1954</t>
   </si>
   <si>
-    <r>
-      <t>290</t>
-    </r>
-  </si>
-  <si>
     <t>EK149</t>
   </si>
   <si>
-    <r>
-      <t>294</t>
-    </r>
-  </si>
-  <si>
     <t>QF640</t>
   </si>
   <si>
-    <r>
-      <t>11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>313</t>
-    </r>
-  </si>
-  <si>
     <t>OS374</t>
   </si>
   <si>
-    <r>
-      <t>330</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>KL184</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>14</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>364</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>IB452</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>377</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>KL123</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>17</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>425</t>
-    </r>
+    <t>KL184</t>
+  </si>
+  <si>
+    <t>IB452</t>
+  </si>
+  <si>
+    <t>KL123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -294,7 +147,7 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="2">
@@ -306,24 +159,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -622,14 +485,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -646,276 +506,276 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" s="3">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>66</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B4" s="3">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3">
+        <v>76</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="3">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
+        <v>108</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B6" s="3">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3">
+        <v>122</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="B7" s="3">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3">
+        <v>141</v>
+      </c>
+      <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" s="3">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B9" s="3">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3">
+        <v>250</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="D4">
+      <c r="B10" s="3">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3">
+        <v>274</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3">
+        <v>290</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3">
+        <v>294</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3">
+        <v>313</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="3">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3">
+        <v>330</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3">
+        <v>364</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="3">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C16" s="3">
+        <v>377</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="3">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
+      <c r="C17" s="3">
+        <v>425</v>
+      </c>
+      <c r="D17" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
+      <c r="E17" s="3">
         <v>1</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
